--- a/dataset_t6_grouped/results2/G4/G4_T1936_W0015F0001T0006Z000C1N66_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T1936_W0015F0001T0006Z000C1N66_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>46.43508706507038</v>
+        <v>7.545701648073938</v>
       </c>
       <c r="D2" t="n">
-        <v>42.99678029125442</v>
+        <v>6.986976797328843</v>
       </c>
       <c r="E2" t="n">
-        <v>15.24825517251674</v>
+        <v>2.47784146553397</v>
       </c>
       <c r="F2" t="n">
-        <v>15.16942776091287</v>
+        <v>2.465032011148341</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>14.56627351665482</v>
+        <v>2.367019446456409</v>
       </c>
       <c r="D3" t="n">
-        <v>10.058112087689</v>
+        <v>1.634443214249463</v>
       </c>
       <c r="E3" t="n">
-        <v>15.24825517251674</v>
+        <v>2.47784146553397</v>
       </c>
       <c r="F3" t="n">
-        <v>15.16942776091287</v>
+        <v>2.465032011148341</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>32.3501846122158</v>
+        <v>5.256904999485068</v>
       </c>
       <c r="D4" t="n">
-        <v>6.479614663549142</v>
+        <v>1.052937382826736</v>
       </c>
       <c r="E4" t="n">
-        <v>15.24825517251674</v>
+        <v>2.47784146553397</v>
       </c>
       <c r="F4" t="n">
-        <v>15.16942776091287</v>
+        <v>2.465032011148341</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>7.45438221881791</v>
+        <v>1.21133711055791</v>
       </c>
       <c r="D5" t="n">
-        <v>7.732884359883605</v>
+        <v>1.256593708481086</v>
       </c>
       <c r="E5" t="n">
-        <v>15.24825517251674</v>
+        <v>2.47784146553397</v>
       </c>
       <c r="F5" t="n">
-        <v>15.16942776091287</v>
+        <v>2.465032011148341</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
